--- a/excel_project/部门考勤数据/宁波分公司（Ningbo Branch）_异常考勤数据.xlsx
+++ b/excel_project/部门考勤数据/宁波分公司（Ningbo Branch）_异常考勤数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25-10-15 星期三</t>
+          <t>25-10-29 星期三</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>丁彬斌-Jimmy Ding</t>
+          <t>李新月-Luna Li</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -515,22 +515,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25-10-10 星期五</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
+          <t>25-11-17 星期一</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>补卡审批通过</t>
+          <t>缺卡</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -542,7 +538,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>彭文涛-Jeff Peng</t>
+          <t>王景江-Andy Wang</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,12 +548,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>25-09-29 星期一</t>
+          <t>25-11-13 星期四</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -565,10 +561,14 @@
           <t>正常</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>缺卡</t>
+          <t>补卡审批通过</t>
         </is>
       </c>
     </row>
@@ -585,12 +585,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25-09-25 星期四</t>
+          <t>25-11-11 星期二</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -612,7 +612,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>吴洁琼-Queeny Wu</t>
+          <t>缪圆霞-Nancy Miao</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25-10-09 星期四</t>
+          <t>25-10-20 星期一</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -637,19 +637,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>补卡审批通过</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>吴洁琼-Queeny Wu</t>
+          <t>缪圆霞-Nancy Miao</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -659,27 +659,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>25-10-17 星期五</t>
+          <t>25-10-21 星期二</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>迟到</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>早退</t>
+          <t>补卡审批通过</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25-09-22 星期一</t>
+          <t>25-10-22 星期三</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>25-09-25 星期四</t>
+          <t>25-10-23 星期四</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>补卡审批通过</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25-09-26 星期五</t>
+          <t>25-10-27 星期一</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>管理员莫良-Peter Mo改为正常</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -807,22 +807,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>25-09-28 星期日</t>
+          <t>25-10-28 星期二</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>迟到</t>
+          <t>补卡审批通过</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>25-09-29 星期一</t>
+          <t>25-11-03 星期一</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>补卡审批通过</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>25-09-30 星期二</t>
+          <t>25-11-04 星期二</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>管理员莫良-Peter Mo改为正常</t>
+          <t>正常</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>25-10-13 星期一</t>
+          <t>25-11-10 星期一</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>25-10-14 星期二</t>
+          <t>25-11-11 星期二</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>25-10-15 星期三</t>
+          <t>25-11-12 星期三</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>25-10-16 星期四</t>
+          <t>25-11-13 星期四</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>25-10-20 星期一</t>
+          <t>25-11-14 星期五</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1081,12 +1081,41 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>正常</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>缪圆霞-Nancy Miao</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>宁波分公司（Ningbo Branch）</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>25-11-20 星期四</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>缺卡</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>未打卡</t>
         </is>
       </c>
     </row>
